--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI13"/>
+  <dimension ref="A1:CI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,69 +893,69 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>116.96</t>
+          <t>117.22</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>148805.0</t>
+          <t>150609.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>81278.2</t>
+          <t>81860.1</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>10587.68</v>
+        <v>5279.75</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,42 +1177,42 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,98 +1419,98 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>116.78</t>
+          <t>116.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>138444.4</t>
+          <t>148805.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>79553.16</t>
+          <t>81278.2</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>9981.799999999999</v>
+        <v>10587.68</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,42 +1608,42 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1698,17 +1698,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,93 +1850,93 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>116.48</t>
+          <t>116.78</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>148242.2</t>
+          <t>138444.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>78905.26</t>
+          <t>79553.16</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>14891.03</v>
+        <v>9981.799999999999</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,42 +2039,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>116.26</t>
+          <t>116.48</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>111.45</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-78.78</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>307249.0</t>
+          <t>139483.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>131919.4</t>
+          <t>148242.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>98993.5</t>
+          <t>110067.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>80710.04</t>
+          <t>78905.26</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>157.3615342815319</t>
+          <t>2424.079051070275</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>15883.66</v>
+        <v>14891.03</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,42 +2470,42 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>120.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>115.94</t>
+          <t>116.26</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>110.76</t>
+          <t>111.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-42.15</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-77.04</t>
+          <t>-78.22</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>63558.0</t>
+          <t>307249.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>87449.2</t>
+          <t>131919.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>71116.7</t>
+          <t>98993.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>75325.82</t>
+          <t>80710.04</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2701.96583734174</t>
+          <t>157.3615342815319</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-1240.49</v>
+        <v>15883.66</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>120.3</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
           <t>122.1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
-      </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>115.82</t>
+          <t>115.94</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.76</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-25.60</t>
+          <t>-42.15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-74.62</t>
+          <t>-77.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>93677.0</t>
+          <t>63558.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>94333.0</t>
+          <t>87449.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>68577.9</t>
+          <t>71116.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>74581.1</t>
+          <t>75325.82</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2967.689129220134</t>
+          <t>-2701.96583734174</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>450.49</v>
+        <v>-1240.49</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>116.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>120.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1129.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,69 +3479,69 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>37.56</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>4.35</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.75</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>31.32</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>122.12</t>
+          <t>122.25</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>115.61</t>
+          <t>115.82</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>110.2</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-25.60</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-72.99</t>
+          <t>-74.62</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>137244.0</t>
+          <t>93677.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>85933.6</t>
+          <t>94333.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>65440.2</t>
+          <t>68577.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>73140.5</t>
+          <t>74581.1</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-3589.177015227112</t>
+          <t>-2967.689129220134</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-376.94</v>
+        <v>450.49</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,42 +3763,42 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>477.0</t>
+          <t>1129.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>121.78</t>
+          <t>122.12</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>115.36</t>
+          <t>115.61</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>109.91</t>
+          <t>110.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-71.75</t>
+          <t>-72.99</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>57869.0</t>
+          <t>137244.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>71893.4</t>
+          <t>85933.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>57057.7</t>
+          <t>65440.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>71210.02</t>
+          <t>73140.5</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-4173.219742776491</t>
+          <t>-3589.177015227112</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-6213.42</v>
+        <v>-376.94</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4194,32 +4194,32 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>477.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,42 +4457,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4502,32 +4502,32 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>121.35</t>
+          <t>121.78</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>115.15</t>
+          <t>115.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>109.62</t>
+          <t>109.91</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>84898.0</t>
+          <t>57869.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>66067.6</t>
+          <t>71893.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>56608.6</t>
+          <t>57057.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>71733.8</t>
+          <t>71210.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3802.273431911177</t>
+          <t>-4173.219742776491</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-5824.88</v>
+        <v>-6213.42</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,79 +4888,79 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>120.85</t>
+          <t>121.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>114.82</t>
+          <t>115.15</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>109.35</t>
+          <t>109.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>2.80</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>9.61</t>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-70.52</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>97977.0</t>
+          <t>84898.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>54784.2</t>
+          <t>66067.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>53768.1</t>
+          <t>56608.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>70942.58</t>
+          <t>71733.8</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3434.52601841664</t>
+          <t>-3802.273431911177</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-7957.76</v>
+        <v>-5824.88</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>421.0</t>
+          <t>782.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-17.62</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>6.58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>592</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>120.28</t>
+          <t>120.85</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>114.43</t>
+          <t>114.82</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>109.05</t>
+          <t>109.35</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-70.42</t>
+          <t>-70.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>252073.1982633864</t>
+          <t>251866.2615606936</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>51680.0</t>
+          <t>97977.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>42822.8</t>
+          <t>54784.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>51980.6</t>
+          <t>53768.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>69368.32</t>
+          <t>70942.58</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-9157</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2612.119945730332</t>
+          <t>-3434.52601841664</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-12121.84</v>
+        <v>-7957.76</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>15.89</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>3.068898097503097</t>
+          <t>-4.149646613080949</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>12.84640767927206</t>
+          <t>13.20370656475155</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>9.4222845618483</t>
+          <t>10.82606207727494</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>23.31</t>
+          <t>21.48</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>9253</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>263.992</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.06</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,288 +5750,4598 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>430</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-4.09</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>55.12</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>56.86</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>59.28</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-28.39</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-1.28</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-0.99</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-113.48</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>29982893.4</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>27325142.8</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>70871687.6</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>2657750</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-4799229.377777515</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>-2145262.02</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>54.2</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>54.6</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>859.439</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-1.31</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>8.38</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-2.41</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-3.95</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>55.72000000000001</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>57.07</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>59.42</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-20.32</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-112.52</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>30810714.6</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>28427276.6</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>71965384.46</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>2383438</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-5281768.897985027</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>-1598621.31</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>-7.53</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>54.0</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-2.3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>952.128</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2.92</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-10.08</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>-2.17</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-3.78</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>56.22000000000001</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>57.31</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>59.56</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>59.23</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-8.99</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-111.89</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>25992585.6</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>25254632.5</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>72823093.42</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>737953</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-5951432.094936458</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>-3313920.55</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>-5.31</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>55.2</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>281.766</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-6.19</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-9.90</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-7.97</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>-1.41</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>18.75</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>8.33</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-0.11</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-3.61</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>56.66</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>57.52</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>59.68</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-2.12</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-111.62</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>20762488.6</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>23044675.4</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>73396602.94</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-2282186</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-6430979.648412267</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>-6293886.05</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>-3.08</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>196.879</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-5.82</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-13.59</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-8.29</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-3.72</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>56.88</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>57.57</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>59.79</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>59.24</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-4.65</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-111.56</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>11143003.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>21951634.2</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>25405032.7</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>75419606.76</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-3453398</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-6455905.757767605</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>-6375046.04</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>-3.42</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>56.8</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>56.9</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>485.041</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-5.63</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-9.51</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-8.46</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>23.08</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-3.66</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>57.06</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>57.72</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>59.92</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>59.23</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-4.50</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-111.42</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>27154672.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>24667392.2</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>27258318.2</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>79188309.68</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-2590926</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-6470607.524677305</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>-5741199.81</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>-3.60</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>55.7</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>56.3</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>401.833</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-6.02</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-8.13</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>49.27</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-3.45</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>57.38</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>57.97</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>60.04</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>59.22</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-111.30</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>22755797.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>26043838.6</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>27711987.6</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>85688285.96</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-1668149</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-6603227.108476495</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>-6346198.32</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>-3.25</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>56.4</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>56.5</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>464.395</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-7.88</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-32.37</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-6.50</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>69.23</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>58.24</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-0.07</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-1.13</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-3.24</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>57.54</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>58.2</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>60.15</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>59.21</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-111.26</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>26742952.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>24516679.4</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>36252527.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>89433496.94</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-11735848</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-6649959.615648801</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>-6512523.92</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>57.5</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>382.341</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-37.15</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-6.18</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>78.57</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>51.83</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-1.81</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-2.91</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>57.36</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>58.42</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-0.37</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-111.36</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>21961747.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>25326862.2</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>40297305.9</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>89685508.6</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-14970443</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-6674947.923535203</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-6944736.97</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>-1.20</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>56.1</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>57.7</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-1.03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>429.27</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-30.09</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-6.83</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-1.75</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
           <t>26.92</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>8.97</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-2.17</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>57.12</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>58.88</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>60.19</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>59.19</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-24.21</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>34.62</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-2.69</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>57.17999999999999</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>58.55</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>59.18</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-7.33</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
         <is>
           <t>7.38</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-110.81</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/09/11</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>340708181.0159091</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>15120001.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>29380136.6</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>42619865.8</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>90864066.74</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-13239729</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-6583586.088250012</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>-7195021.75</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-111.35</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>24721793.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>28858431.2</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>41279456.2</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>89986915.22</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-12421025</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-6625895.370469017</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>-6801885.89</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
         <is>
           <t>58.4</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BF22" t="inlineStr">
         <is>
           <t>2025/08/13</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>-1.88</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BH22" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BI22" t="inlineStr">
         <is>
           <t>凌群</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>資訊服務業</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>0.93</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>1.421423718361266</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>9.706318657345912</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>7.884764051476033</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BR22" t="inlineStr">
         <is>
           <t>2.69</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>4.81</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
         <is>
           <t>18.50</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>16.98</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
         <is>
           <t>25.81%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BW22" t="inlineStr">
         <is>
           <t>3.37%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>28.74</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
         <is>
           <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CA22" t="inlineStr">
         <is>
           <t>凌群-資訊服務業-上市</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>資訊服務業平上市</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>57.6</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>56.8</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>58.1</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>58.3</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
         <is>
           <t>57.3</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>57.3</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
         <is>
           <t>21.28</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CH22" t="inlineStr">
         <is>
           <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>585.383</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-8.63</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-29.49</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-5.85</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>0.74</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>25.64</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-2.62</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-2.46</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>57.16</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>58.7</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>60.17</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>59.2</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-11.72</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>7.38</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-111.14</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/11/06</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>335809734.6773472</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>34036904.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>29849244.2</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>42331695.0</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>90805826.98</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-12482450</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-6593897.095029591</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>-6650607.63</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>58.4</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>凌群</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>-13.01541036036408</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>5.576499396182672</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>7.68516930639722</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>2.72</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>18.50</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>25.81%</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>3.37%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>28.27</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>電腦週邊設備及系統整合77.00%、電腦設備維修23.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>凌群-資訊服務業-上市</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>資訊服務業右下上市</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>57.8</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>58.8</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>57.1</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>57.9</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>21.28</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>** 軟體服務 - 應用/系統軟體設計開發、系統整合服務、資料處理服務、通路經銷** 太空衛星科技 - 通訊、影像遙測、導航定位** 區塊鏈 - 交易平台、商業應用、錢包/資產管理、BaaS、系統整合、領域方案、底層平台、開發工具、監控管理、創投、顧問諮詢、媒體推廣、資安審計** 金融科技 - 保險、支付、數位銀行、監理法遵、理財投資、加密資產、數據分析、資料聚合、數位身分** 人工智慧 - 系統整合、領域解決方案** 雲端運算 - 系統整合、設備安裝服務** 資通訊安全 - 資安顧問服務** 大數據 - 系統整合、顧問諮詢、領域解決方案、資料庫、分析工具、應用軟體、儲存處理</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>117.22</t>
+          <t>117.41</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>150609.8</t>
+          <t>101382.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>81860.1</t>
+          <t>82649.4</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>5279.75</v>
+        <v>572.11</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,69 +1324,69 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-2.94</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>116.96</t>
+          <t>117.22</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>148805.0</t>
+          <t>150609.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>81278.2</t>
+          <t>81860.1</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>10587.68</v>
+        <v>5279.75</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,22 +1850,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>116.78</t>
+          <t>116.96</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>138444.4</t>
+          <t>148805.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>79553.16</t>
+          <t>81278.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>9981.799999999999</v>
+        <v>10587.68</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,22 +2281,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -2307,67 +2307,67 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>116.48</t>
+          <t>116.78</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>148242.2</t>
+          <t>138444.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>78905.26</t>
+          <t>79553.16</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>14891.03</v>
+        <v>9981.799999999999</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-5.46</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,72 +2738,72 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>116.26</t>
+          <t>116.48</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>111.45</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-78.78</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>307249.0</t>
+          <t>139483.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>131919.4</t>
+          <t>148242.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>98993.5</t>
+          <t>110067.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>80710.04</t>
+          <t>78905.26</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>157.3615342815319</t>
+          <t>2424.079051070275</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>15883.66</v>
+        <v>14891.03</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>120.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>115.94</t>
+          <t>116.26</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>110.76</t>
+          <t>111.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-42.15</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-77.04</t>
+          <t>-78.22</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>63558.0</t>
+          <t>307249.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>87449.2</t>
+          <t>131919.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>71116.7</t>
+          <t>98993.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>75325.82</t>
+          <t>80710.04</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2701.96583734174</t>
+          <t>157.3615342815319</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-1240.49</v>
+        <v>15883.66</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>120.3</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
           <t>122.1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
-      </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>115.82</t>
+          <t>115.94</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.76</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-25.60</t>
+          <t>-42.15</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-74.62</t>
+          <t>-77.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>93677.0</t>
+          <t>63558.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>94333.0</t>
+          <t>87449.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>68577.9</t>
+          <t>71116.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>74581.1</t>
+          <t>75325.82</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2967.689129220134</t>
+          <t>-2701.96583734174</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>450.49</v>
+        <v>-1240.49</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>116.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>120.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1129.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,69 +3910,69 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.84</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-1.35</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>37.56</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.61</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>31.32</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>122.12</t>
+          <t>122.25</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>115.61</t>
+          <t>115.82</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>110.2</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-25.60</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-72.99</t>
+          <t>-74.62</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>137244.0</t>
+          <t>93677.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>85933.6</t>
+          <t>94333.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>65440.2</t>
+          <t>68577.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>73140.5</t>
+          <t>74581.1</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-3589.177015227112</t>
+          <t>-2967.689129220134</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-376.94</v>
+        <v>450.49</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>477.0</t>
+          <t>1129.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>121.78</t>
+          <t>122.12</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>115.36</t>
+          <t>115.61</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>109.91</t>
+          <t>110.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-71.75</t>
+          <t>-72.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>57869.0</t>
+          <t>137244.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>71893.4</t>
+          <t>85933.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>57057.7</t>
+          <t>65440.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>71210.02</t>
+          <t>73140.5</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-4173.219742776491</t>
+          <t>-3589.177015227112</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-6213.42</v>
+        <v>-376.94</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,17 +4710,17 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>477.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,37 +4893,37 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4933,32 +4933,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>121.35</t>
+          <t>121.78</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>115.15</t>
+          <t>115.36</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>109.62</t>
+          <t>109.91</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>84898.0</t>
+          <t>57869.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>66067.6</t>
+          <t>71893.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>56608.6</t>
+          <t>57057.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>71733.8</t>
+          <t>71210.02</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3802.273431911177</t>
+          <t>-4173.219742776491</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-5824.88</v>
+        <v>-6213.42</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>782.0</t>
+          <t>687.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,74 +5324,74 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>507</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.38</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>122.8</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>120.85</t>
+          <t>121.35</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>114.82</t>
+          <t>115.15</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>109.35</t>
+          <t>109.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>2.67</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
           <t>2.80</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>9.61</t>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-70.52</t>
+          <t>-70.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>251866.2615606936</t>
+          <t>251635.0995670995</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>97977.0</t>
+          <t>84898.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>54784.2</t>
+          <t>66067.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53768.1</t>
+          <t>56608.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>70942.58</t>
+          <t>71733.8</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3434.52601841664</t>
+          <t>-3802.273431911177</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-7957.76</v>
+        <v>-5824.88</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>17.92</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>21.48</t>
+          <t>21.14</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,42 +6196,42 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6241,17 +6241,17 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.19</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,17 +7043,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7063,59 +7063,59 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.82</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,57 +7474,57 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -7534,17 +7534,17 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7732,17 +7732,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-8.48</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,64 +8351,64 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.88</t>
+          <t>-8.86</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,72 +8767,72 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-10.79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>429.27</t>
+          <t>382.341</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>-11.18</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-37.15</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,52 +9629,52 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>51.83</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.17999999999999</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>58.55</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -9684,17 +9684,17 @@
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.18</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-111.36</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>24721793.0</t>
+          <t>21961747.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>28858431.2</t>
+          <t>25326862.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>41279456.2</t>
+          <t>40297305.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>89986915.22</t>
+          <t>89685508.6</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-12421025</t>
+          <t>-14970443</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6625895.370469017</t>
+          <t>-6674947.923535203</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6801885.89</v>
+        <v>-6944736.97</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>585.383</t>
+          <t>429.27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-10.4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-30.09</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,52 +10060,52 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>805</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>26.92</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>34.62</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.62</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.16</t>
+          <t>57.17999999999999</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>58.55</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,22 +10115,22 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.18</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.72</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.14</t>
+          <t>-111.35</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>335809734.6773472</t>
+          <t>335403933.5290179</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>34036904.0</t>
+          <t>24721793.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>29849244.2</t>
+          <t>28858431.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>42331695.0</t>
+          <t>41279456.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>90805826.98</t>
+          <t>89986915.22</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-12482450</t>
+          <t>-12421025</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6593897.095029591</t>
+          <t>-6625895.370469017</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6650607.63</v>
+        <v>-6801885.89</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>121.85</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>117.41</t>
+          <t>117.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>101382.8</t>
+          <t>87842.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>82649.4</t>
+          <t>83455.92</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>572.11</v>
+        <v>-1937.52</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>117.22</t>
+          <t>117.41</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>150609.8</t>
+          <t>101382.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>81860.1</t>
+          <t>82649.4</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>5279.75</v>
+        <v>572.11</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,69 +1755,69 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-5.15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>116.96</t>
+          <t>117.22</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>148805.0</t>
+          <t>150609.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>81278.2</t>
+          <t>81860.1</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>10587.68</v>
+        <v>5279.75</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,98 +2281,98 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>116.78</t>
+          <t>116.96</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>138444.4</t>
+          <t>148805.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>79553.16</t>
+          <t>81278.2</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>9981.799999999999</v>
+        <v>10587.68</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.46</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,93 +2712,93 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>116.48</t>
+          <t>116.78</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>148242.2</t>
+          <t>138444.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>78905.26</t>
+          <t>79553.16</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>14891.03</v>
+        <v>9981.799999999999</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-7.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>116.26</t>
+          <t>116.48</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>111.45</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-78.78</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>307249.0</t>
+          <t>139483.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>131919.4</t>
+          <t>148242.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>98993.5</t>
+          <t>110067.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>80710.04</t>
+          <t>78905.26</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>157.3615342815319</t>
+          <t>2424.079051070275</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>15883.66</v>
+        <v>14891.03</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>-8.58</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>120.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>115.94</t>
+          <t>116.26</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>110.76</t>
+          <t>111.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-42.15</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-77.04</t>
+          <t>-78.22</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>63558.0</t>
+          <t>307249.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>87449.2</t>
+          <t>131919.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>71116.7</t>
+          <t>98993.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>75325.82</t>
+          <t>80710.04</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-2701.96583734174</t>
+          <t>157.3615342815319</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-1240.49</v>
+        <v>15883.66</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>120.3</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
           <t>122.1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
-      </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>115.82</t>
+          <t>115.94</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.76</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-25.60</t>
+          <t>-42.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-74.62</t>
+          <t>-77.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>93677.0</t>
+          <t>63558.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>94333.0</t>
+          <t>87449.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>68577.9</t>
+          <t>71116.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>74581.1</t>
+          <t>75325.82</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2967.689129220134</t>
+          <t>-2701.96583734174</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>450.49</v>
+        <v>-1240.49</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>116.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>120.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1129.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,69 +4341,69 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-3.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-3.75</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>37.56</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.68</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>31.32</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>122.12</t>
+          <t>122.25</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>115.61</t>
+          <t>115.82</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>110.2</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-25.60</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-72.99</t>
+          <t>-74.62</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>137244.0</t>
+          <t>93677.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>85933.6</t>
+          <t>94333.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>65440.2</t>
+          <t>68577.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>73140.5</t>
+          <t>74581.1</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-3589.177015227112</t>
+          <t>-2967.689129220134</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-376.94</v>
+        <v>450.49</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>477.0</t>
+          <t>1129.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>121.78</t>
+          <t>122.12</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>115.36</t>
+          <t>115.61</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>109.91</t>
+          <t>110.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-71.75</t>
+          <t>-72.99</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>57869.0</t>
+          <t>137244.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>71893.4</t>
+          <t>85933.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>57057.7</t>
+          <t>65440.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>71210.02</t>
+          <t>73140.5</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-4173.219742776491</t>
+          <t>-3589.177015227112</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-6213.42</v>
+        <v>-376.94</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>687.0</t>
+          <t>477.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,42 +5319,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>615</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
           <t>50.0</t>
         </is>
       </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>83.33</t>
-        </is>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5364,32 +5364,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>121.35</t>
+          <t>121.78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>115.15</t>
+          <t>115.36</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>109.62</t>
+          <t>109.91</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-12.53</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-70.87</t>
+          <t>-71.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>251635.0995670995</t>
+          <t>251427.659221902</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>84898.0</t>
+          <t>57869.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>66067.6</t>
+          <t>71893.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>56608.6</t>
+          <t>57057.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>71733.8</t>
+          <t>71210.02</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>14835</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-3802.273431911177</t>
+          <t>-4173.219742776491</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-5824.88</v>
+        <v>-6213.42</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>14.95</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>17.92</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8522</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-1044878.26</v>
+        <v>-1885548.44</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,42 +6627,42 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-4.45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,17 +7474,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7494,59 +7494,59 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,57 +7905,57 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7965,17 +7965,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8163,17 +8163,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-9.09</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.86</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,64 +8782,64 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.79</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,72 +9198,72 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-11.18</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>429.27</t>
+          <t>382.341</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.4</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-30.09</t>
+          <t>-37.15</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>-6.18</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,52 +10060,52 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>392</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>34.62</t>
+          <t>51.83</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.17999999999999</t>
+          <t>57.36</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>58.55</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -10115,17 +10115,17 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.18</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.35</t>
+          <t>-111.36</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>335403933.5290179</t>
+          <t>334950688.6760772</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>24721793.0</t>
+          <t>21961747.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>28858431.2</t>
+          <t>25326862.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>41279456.2</t>
+          <t>40297305.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>89986915.22</t>
+          <t>89685508.6</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-12421025</t>
+          <t>-14970443</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6625895.370469017</t>
+          <t>-6674947.923535203</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6801885.89</v>
+        <v>-6944736.97</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5170</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>121.85</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>117.54</t>
+          <t>117.76</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>87842.4</t>
+          <t>78379.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>83455.92</t>
+          <t>83812.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-1937.52</v>
+        <v>-5959.05</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.15</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>121.85</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>117.41</t>
+          <t>117.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>101382.8</t>
+          <t>87842.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>82649.4</t>
+          <t>83455.92</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>572.11</v>
+        <v>-1937.52</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>117.22</t>
+          <t>117.41</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>150609.8</t>
+          <t>101382.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>81860.1</t>
+          <t>82649.4</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>5279.75</v>
+        <v>572.11</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,69 +2186,69 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-3.86</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-3.75</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>116.96</t>
+          <t>117.22</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>148805.0</t>
+          <t>150609.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>81278.2</t>
+          <t>81860.1</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>10587.68</v>
+        <v>5279.75</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,98 +2712,98 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>116.78</t>
+          <t>116.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>138444.4</t>
+          <t>148805.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>79553.16</t>
+          <t>81278.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>9981.799999999999</v>
+        <v>10587.68</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.73</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,93 +3143,93 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>116.48</t>
+          <t>116.78</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>148242.2</t>
+          <t>138444.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>78905.26</t>
+          <t>79553.16</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>14891.03</v>
+        <v>9981.799999999999</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.58</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>116.26</t>
+          <t>116.48</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>111.45</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-78.78</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>307249.0</t>
+          <t>139483.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>131919.4</t>
+          <t>148242.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>98993.5</t>
+          <t>110067.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>80710.04</t>
+          <t>78905.26</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>157.3615342815319</t>
+          <t>2424.079051070275</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>15883.66</v>
+        <v>14891.03</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>120.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>115.94</t>
+          <t>116.26</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>110.76</t>
+          <t>111.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-42.15</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-77.04</t>
+          <t>-78.22</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>63558.0</t>
+          <t>307249.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>87449.2</t>
+          <t>131919.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>71116.7</t>
+          <t>98993.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>75325.82</t>
+          <t>80710.04</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-2701.96583734174</t>
+          <t>157.3615342815319</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-1240.49</v>
+        <v>15883.66</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>120.3</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
           <t>122.1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
-      </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>115.82</t>
+          <t>115.94</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.76</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-25.60</t>
+          <t>-42.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-74.62</t>
+          <t>-77.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>93677.0</t>
+          <t>63558.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>94333.0</t>
+          <t>87449.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>68577.9</t>
+          <t>71116.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>74581.1</t>
+          <t>75325.82</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-2967.689129220134</t>
+          <t>-2701.96583734174</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>450.49</v>
+        <v>-1240.49</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>116.5</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>120.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1129.0</t>
+          <t>790.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,69 +4772,69 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>37.56</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-3.86</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-3.75</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>31.32</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>6.65</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>122.12</t>
+          <t>122.25</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>115.61</t>
+          <t>115.82</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>110.2</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-18.36</t>
+          <t>-25.60</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-72.99</t>
+          <t>-74.62</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>137244.0</t>
+          <t>93677.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>85933.6</t>
+          <t>94333.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>65440.2</t>
+          <t>68577.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>73140.5</t>
+          <t>74581.1</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>25755</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-3589.177015227112</t>
+          <t>-2967.689129220134</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-376.94</v>
+        <v>450.49</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>477.0</t>
+          <t>1129.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>121.78</t>
+          <t>122.12</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>115.36</t>
+          <t>115.61</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>109.91</t>
+          <t>110.2</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.53</t>
+          <t>-18.36</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-71.75</t>
+          <t>-72.99</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>251427.659221902</t>
+          <t>251154.2482014388</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>57869.0</t>
+          <t>137244.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>71893.4</t>
+          <t>85933.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>57057.7</t>
+          <t>65440.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>71210.02</t>
+          <t>73140.5</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>20493</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-4173.219742776491</t>
+          <t>-3589.177015227112</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-6213.42</v>
+        <v>-376.94</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>18.3</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>21.51</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,17 +5572,17 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5755,72 +5755,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-1885548.44</v>
+        <v>-3089720.84</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-1044878.26</v>
+        <v>-1885548.44</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-2145262.02</v>
+        <v>-1044878.26</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,42 +7058,42 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7103,17 +7103,17 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-1598621.31</v>
+        <v>-2145262.02</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-3313920.55</v>
+        <v>-1598621.31</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7910,12 +7910,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7925,59 +7925,59 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-6293886.05</v>
+        <v>-3313920.55</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.09</t>
+          <t>-7.81</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8341,52 +8341,52 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8396,17 +8396,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-6375046.04</v>
+        <v>-6293886.05</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8772,72 +8772,72 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-5741199.81</v>
+        <v>-6375046.04</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-7.24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,64 +9213,64 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-6346198.32</v>
+        <v>-5741199.81</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>464.395</t>
+          <t>401.833</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-7.62</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.37</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-8.13</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9634,67 +9634,67 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>69.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>49.27</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.24</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.54</t>
+          <t>57.38</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.97</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>60.15</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.21</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.80</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.26</t>
+          <t>-111.30</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>26742952.0</t>
+          <t>22755797.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24516679.4</t>
+          <t>26043838.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>36252527.7</t>
+          <t>27711987.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>89433496.94</t>
+          <t>85688285.96</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-11735848</t>
+          <t>-1668149</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6649959.615648801</t>
+          <t>-6603227.108476495</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-6512523.92</v>
+        <v>-6346198.32</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>382.341</t>
+          <t>464.395</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-11.61</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-37.15</t>
+          <t>-32.37</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-6.18</t>
+          <t>-6.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10065,72 +10065,72 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>218</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>78.57</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>51.83</t>
+          <t>58.24</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.81</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.24</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.36</t>
+          <t>57.54</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.17</t>
+          <t>60.15</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.21</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.36</t>
+          <t>-111.26</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>334950688.6760772</t>
+          <t>334479119.8620178</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>21961747.0</t>
+          <t>26742952.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>25326862.2</t>
+          <t>24516679.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>40297305.9</t>
+          <t>36252527.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>89685508.6</t>
+          <t>89433496.94</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-14970443</t>
+          <t>-11735848</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6674947.923535203</t>
+          <t>-6649959.615648801</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-6944736.97</v>
+        <v>-6512523.92</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>5170</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>57.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,27 +1014,27 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>117.93</t>
+          <t>118.09</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>58524.2</t>
+          <t>52439.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>84131.76</t>
+          <t>83734.12</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>46206</v>
+        <v>42160</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.88</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>117.76</t>
+          <t>117.93</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>78379.0</t>
+          <t>58524.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>83812.18</t>
+          <t>84131.76</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>40938</v>
+        <v>46206</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>121.85</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>117.54</t>
+          <t>117.76</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>87842.4</t>
+          <t>78379.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>83455.92</t>
+          <t>83812.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>71781</v>
+        <v>40938</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>121.85</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>117.41</t>
+          <t>117.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>101382.8</t>
+          <t>87842.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>82649.4</t>
+          <t>83455.92</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>61114</v>
+        <v>71781</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>117.22</t>
+          <t>117.41</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>150609.8</t>
+          <t>101382.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>81860.1</t>
+          <t>82649.4</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>5279.749565520178</t>
+          <t>572.1051821399305</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>72582</v>
+        <v>61114</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,69 +3078,69 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-1.64</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.41</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.74</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>116.96</t>
+          <t>117.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>148805.0</t>
+          <t>150609.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>81278.2</t>
+          <t>81860.1</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>10587.67905729481</t>
+          <t>5279.749565520178</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>145480</v>
+        <v>72582</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,98 +3609,98 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>116.78</t>
+          <t>116.96</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>138444.4</t>
+          <t>148805.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>79553.16</t>
+          <t>81278.2</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>9981.804079212336</t>
+          <t>10587.67905729481</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>88255</v>
+        <v>145480</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3893,17 +3893,17 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,93 +4045,93 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>116.48</t>
+          <t>116.78</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>148242.2</t>
+          <t>138444.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>78905.26</t>
+          <t>79553.16</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>14891.02539340836</t>
+          <t>9981.804079212336</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>139483</v>
+        <v>88255</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>116.26</t>
+          <t>116.48</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>111.45</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-78.78</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>307249.0</t>
+          <t>139483.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>131919.4</t>
+          <t>148242.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>98993.5</t>
+          <t>110067.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>80710.04</t>
+          <t>78905.26</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>157.3615342815319</t>
+          <t>2424.079051070275</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>15883.66207820953</t>
+          <t>14891.02539340836</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>307249</v>
+        <v>139483</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>120.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>115.94</t>
+          <t>116.26</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>110.76</t>
+          <t>111.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-42.15</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.04</t>
+          <t>-78.22</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>63558.0</t>
+          <t>307249.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>87449.2</t>
+          <t>131919.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>71116.7</t>
+          <t>98993.5</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>75325.82</t>
+          <t>80710.04</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-2701.96583734174</t>
+          <t>157.3615342815319</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1240.487732010573</t>
+          <t>15883.66207820953</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>63558</v>
+        <v>307249</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>790.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>22.97</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>343</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
+          <t>120.3</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
           <t>122.1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>122.25</t>
-        </is>
-      </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>115.82</t>
+          <t>115.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>110.76</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-25.60</t>
+          <t>-42.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.62</t>
+          <t>-77.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>250892.9762931034</t>
+          <t>250623.7467718795</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>93677.0</t>
+          <t>63558.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>94333.0</t>
+          <t>87449.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>68577.9</t>
+          <t>71116.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>74581.1</t>
+          <t>75325.82</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>25755</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2967.689129220134</t>
+          <t>-2701.96583734174</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>450.4942438182479</t>
+          <t>-1240.487732010573</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>93677</v>
+        <v>63558</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>18.15</t>
+          <t>18.45</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>21.21</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8961</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>116.5</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>120.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,17 +6439,17 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,17 +6875,17 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,42 +8005,42 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8050,17 +8050,17 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-7.8</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,17 +8862,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8882,59 +8882,59 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-10.33</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,57 +9298,57 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9561,17 +9561,17 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-5741199.813781753</t>
+          <t>-6375046.039764259</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>27154672</v>
+        <v>11143003</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>401.833</t>
+          <t>485.041</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.14</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.13</t>
+          <t>-8.46</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>307</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,64 +10185,64 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>49.27</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-3.66</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.38</t>
+          <t>57.06</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.97</t>
+          <t>57.72</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>59.92</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-4.50</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.84</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.83</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.30</t>
+          <t>-111.42</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>334021433.7844445</t>
+          <t>333562435.6087278</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>22755797.0</t>
+          <t>27154672.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>26043838.6</t>
+          <t>24667392.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27711987.6</t>
+          <t>27258318.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>85688285.96</t>
+          <t>79188309.68</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1668149</t>
+          <t>-2590926</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6603227.108476495</t>
+          <t>-6470607.524677305</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-6346198.319028817</t>
+          <t>-5741199.813781753</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>22755797</v>
+        <v>27154672</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-3.60</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>28.04</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.5</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>343.0</t>
+          <t>529.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-48.35</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>121.88</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>118.09</t>
+          <t>118.31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>114.14</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>52439.8</t>
+          <t>53388.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>101524.8</t>
+          <t>77385.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>83734.12</t>
+          <t>83948.7</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-49085</t>
+          <t>-23997</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-1324.899258908528</t>
+          <t>-2516.965009164283</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9917.436921404122</t>
+          <t>-9073.326635570935</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>42160</v>
+        <v>65858</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,27 +1450,27 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>117.93</t>
+          <t>118.09</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>58524.2</t>
+          <t>52439.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>84131.76</t>
+          <t>83734.12</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>46206</v>
+        <v>42160</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.88</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>117.76</t>
+          <t>117.93</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>78379.0</t>
+          <t>58524.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>83812.18</t>
+          <t>84131.76</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>40938</v>
+        <v>46206</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>121.85</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>117.54</t>
+          <t>117.76</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>87842.4</t>
+          <t>78379.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>83455.92</t>
+          <t>83812.18</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>71781</v>
+        <v>40938</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>121.85</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>117.41</t>
+          <t>117.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>101382.8</t>
+          <t>87842.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>82649.4</t>
+          <t>83455.92</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>61114</v>
+        <v>71781</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>117.22</t>
+          <t>117.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>150609.8</t>
+          <t>101382.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>81860.1</t>
+          <t>82649.4</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>5279.749565520178</t>
+          <t>572.1051821399305</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>72582</v>
+        <v>61114</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,69 +3514,69 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-09-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-09-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.22</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>-1.64</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>116.96</t>
+          <t>117.22</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>148805.0</t>
+          <t>150609.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>81278.2</t>
+          <t>81860.1</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>10587.67905729481</t>
+          <t>5279.749565520178</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>145480</v>
+        <v>72582</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,98 +4045,98 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>116.78</t>
+          <t>116.96</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>138444.4</t>
+          <t>148805.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>79553.16</t>
+          <t>81278.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>9981.804079212336</t>
+          <t>10587.67905729481</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>88255</v>
+        <v>145480</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,93 +4481,93 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>116.48</t>
+          <t>116.78</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>148242.2</t>
+          <t>138444.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>78905.26</t>
+          <t>79553.16</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>14891.02539340836</t>
+          <t>9981.804079212336</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>139483</v>
+        <v>88255</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>116.26</t>
+          <t>116.48</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>111.45</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-78.78</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>307249.0</t>
+          <t>139483.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>131919.4</t>
+          <t>148242.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>98993.5</t>
+          <t>110067.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>80710.04</t>
+          <t>78905.26</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>157.3615342815319</t>
+          <t>2424.079051070275</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>15883.66207820953</t>
+          <t>14891.02539340836</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>307249</v>
+        <v>139483</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>8.06</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>2432.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.97</t>
+          <t>33.26</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>20.46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>529</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>120.3</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>121.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>115.94</t>
+          <t>116.26</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>110.76</t>
+          <t>111.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-42.15</t>
+          <t>-21.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-77.04</t>
+          <t>-78.22</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>250623.7467718795</t>
+          <t>250406.2156160459</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>63558.0</t>
+          <t>307249.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>87449.2</t>
+          <t>131919.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>71116.7</t>
+          <t>98993.5</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>75325.82</t>
+          <t>80710.04</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-2701.96583734174</t>
+          <t>157.3615342815319</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-1240.487732010573</t>
+          <t>15883.66207820953</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>63558</v>
+        <v>307249</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>18.45</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>21.59</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,42 +5679,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>274.793</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>51.9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>307.156</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,42 +5810,42 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5855,32 +5855,32 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>21316600.4</t>
+          <t>15743790.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>67714501.66</t>
+          <t>65312254.98</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>15825778</v>
+        <v>14210191</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,12 +6246,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,17 +6504,17 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,42 +8441,42 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -8486,17 +8486,17 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.8</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.33</t>
+          <t>-6.55</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,17 +9298,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9318,59 +9318,59 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,57 +9734,57 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -9794,17 +9794,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9997,17 +9997,17 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>485.041</t>
+          <t>196.879</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-13.59</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.46</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>275</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>57.06</t>
+          <t>56.88</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.72</t>
+          <t>57.57</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.92</t>
+          <t>59.79</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.24</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.50</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.42</t>
+          <t>-111.56</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>333562435.6087278</t>
+          <t>333101213.8227474</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>27154672.0</t>
+          <t>11143003.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>24667392.2</t>
+          <t>21951634.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27258318.2</t>
+          <t>25405032.7</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>79188309.68</t>
+          <t>75419606.76</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2590926</t>
+          <t>-3453398</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6470607.524677305</t>
+          <t>-6455905.757767605</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-5741199.813781753</t>
+          <t>-6375046.039764259</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>27154672</v>
+        <v>11143003</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.60</t>
+          <t>-3.42</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.13</t>
+          <t>16.32</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>529.0</t>
+          <t>418.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-27.88</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -933,158 +933,158 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.3</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>118.31</t>
+          <t>118.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>114.14</t>
+          <t>114.51</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,60 +1094,60 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-89.20</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>53388.6</t>
+          <t>49543.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>77385.7</t>
+          <t>68693.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>83948.7</t>
+          <t>83815.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-23997</t>
+          <t>-19149</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-2516.965009164283</t>
+          <t>-3553.307510769535</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9073.326635570935</t>
+          <t>-9253.191269598421</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>65858</v>
+        <v>52557</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>343.0</t>
+          <t>529.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-48.35</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1369,49 +1369,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1419,27 +1419,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>121.88</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>118.09</t>
+          <t>118.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>114.14</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,56 +1530,56 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>52439.8</t>
+          <t>53388.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>101524.8</t>
+          <t>77385.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>83734.12</t>
+          <t>83948.7</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-49085</t>
+          <t>-23997</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-1324.899258908528</t>
+          <t>-2516.965009164283</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9917.436921404122</t>
+          <t>-9073.326635570935</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>42160</v>
+        <v>65858</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1805,49 +1805,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1855,27 +1855,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,27 +1886,27 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1936,27 +1936,27 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>117.93</t>
+          <t>118.09</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,56 +1966,56 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>58524.2</t>
+          <t>52439.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>84131.76</t>
+          <t>83734.12</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>46206</v>
+        <v>42160</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2241,49 +2241,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2291,27 +2291,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>121.88</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>117.76</t>
+          <t>117.93</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,56 +2402,56 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>78379.0</t>
+          <t>58524.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>83812.18</t>
+          <t>84131.76</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>40938</v>
+        <v>46206</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2677,49 +2677,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2727,27 +2727,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>121.85</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>117.54</t>
+          <t>117.76</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,56 +2838,56 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>87842.4</t>
+          <t>78379.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>83455.92</t>
+          <t>83812.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>71781</v>
+        <v>40938</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3113,49 +3113,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3163,27 +3163,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>121.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>117.41</t>
+          <t>117.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,56 +3274,56 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>101382.8</t>
+          <t>87842.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>82649.4</t>
+          <t>83455.92</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>61114</v>
+        <v>71781</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3549,49 +3549,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3599,27 +3599,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>117.22</t>
+          <t>117.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,56 +3710,56 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>150609.8</t>
+          <t>101382.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>81860.1</t>
+          <t>82649.4</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>5279.749565520178</t>
+          <t>572.1051821399305</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>72582</v>
+        <v>61114</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,84 +3950,84 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -4035,27 +4035,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>116.96</t>
+          <t>117.22</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,56 +4146,56 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>148805.0</t>
+          <t>150609.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>81278.2</t>
+          <t>81860.1</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10587.67905729481</t>
+          <t>5279.749565520178</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>145480</v>
+        <v>72582</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4421,49 +4421,49 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4471,108 +4471,108 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>122.2</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>116.78</t>
+          <t>116.96</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,56 +4582,56 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>138444.4</t>
+          <t>148805.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>79553.16</t>
+          <t>81278.2</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>9981.804079212336</t>
+          <t>10587.67905729481</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>88255</v>
+        <v>145480</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,49 +4857,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4907,103 +4907,103 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>122.15</t>
+          <t>122.2</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>116.48</t>
+          <t>116.78</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5018,56 +5018,56 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>148242.2</t>
+          <t>138444.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>78905.26</t>
+          <t>79553.16</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>14891.02539340836</t>
+          <t>9981.804079212336</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>139483</v>
+        <v>88255</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2432.0</t>
+          <t>1107.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33.26</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5293,49 +5293,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-10-23 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>114.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>114.5</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>113.5</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5343,27 +5343,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>121.95</t>
+          <t>122.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>116.26</t>
+          <t>116.48</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>111.12</t>
+          <t>111.45</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-21.73</t>
+          <t>-10.59</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,56 +5454,56 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-78.22</t>
+          <t>-78.78</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/01</t>
+          <t>2025/11/26</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>250406.2156160459</t>
+          <t>250160.7639484979</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>307249.0</t>
+          <t>139483.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>131919.4</t>
+          <t>148242.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>98993.5</t>
+          <t>110067.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>80710.04</t>
+          <t>78905.26</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>157.3615342815319</t>
+          <t>2424.079051070275</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>15883.66207820953</t>
+          <t>14891.02539340836</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>307249</v>
+        <v>139483</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>21.59</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9180</t>
+          <t>9143</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5815,72 +5815,72 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>55.01</t>
+          <t>54.78</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>58.25</t>
+          <t>58.02</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>15743790.2</t>
+          <t>14968564.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>65312254.98</t>
+          <t>55328963.9</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>14210191</v>
+        <v>16370637</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6251,37 +6251,37 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -6291,32 +6291,32 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>55.27</t>
+          <t>55.01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>58.46</t>
+          <t>58.25</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21316600.4</t>
+          <t>15743790.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>67714501.66</t>
+          <t>65312254.98</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>15825778</v>
+        <v>14210191</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>55.27</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>58.66</t>
+          <t>58.46</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22754558.0</t>
+          <t>21316600.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>69191727.6</t>
+          <t>67714501.66</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>17027345</v>
+        <v>15825778</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,17 +6940,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>55.92</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>58.83</t>
+          <t>58.66</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>28718377.4</t>
+          <t>22754558.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>69373581.34</t>
+          <t>69191727.6</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>11408872</v>
+        <v>17027345</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,127 +7423,127 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>217.689</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>-0.38</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>392.184</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-3.02</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>4.98</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-14.63</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>0.39</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-4.66</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>28.13</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>-15.93</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>0.21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7559,72 +7559,72 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>56.26</t>
+          <t>55.92</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>58.96</t>
+          <t>58.83</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>37015290.4</t>
+          <t>28718377.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>69945836.02</t>
+          <t>69373581.34</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>20246765</v>
+        <v>11408872</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>56.57</t>
+          <t>56.26</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>59.12</t>
+          <t>58.96</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>36169141.2</t>
+          <t>37015290.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>70323701.58</t>
+          <t>69945836.02</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>42074242</v>
+        <v>20246765</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>56.57</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>59.28</t>
+          <t>59.12</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>29982893.4</t>
+          <t>36169141.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>70871687.6</t>
+          <t>70323701.58</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>23015566</v>
+        <v>42074242</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,42 +8877,42 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>57.07</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>59.42</t>
+          <t>59.28</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -8922,17 +8922,17 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>30810714.6</t>
+          <t>29982893.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>71965384.46</t>
+          <t>70871687.6</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>46846442</v>
+        <v>23015566</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.55</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9313,62 +9313,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>57.31</t>
+          <t>57.07</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>59.56</t>
+          <t>59.42</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>25992585.6</t>
+          <t>30810714.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>72823093.42</t>
+          <t>71965384.46</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>52893437</v>
+        <v>46846442</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-5.74</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9739,12 +9739,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9754,59 +9754,59 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>57.52</t>
+          <t>57.31</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>59.68</t>
+          <t>59.56</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>20762488.6</t>
+          <t>25992585.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>73396602.94</t>
+          <t>72823093.42</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>16016019</v>
+        <v>52893437</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>196.879</t>
+          <t>281.766</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-8.22</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-9.90</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10175,52 +10175,52 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>313</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>18.75</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>56.88</t>
+          <t>56.66</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>57.57</t>
+          <t>57.52</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>59.68</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -10230,17 +10230,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.56</t>
+          <t>-111.62</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>333101213.8227474</t>
+          <t>332646132.3207964</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>11143003.0</t>
+          <t>16016019.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>21951634.2</t>
+          <t>20762488.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>25405032.7</t>
+          <t>23044675.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>75419606.76</t>
+          <t>73396602.94</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3453398</t>
+          <t>-2282186</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6455905.757767605</t>
+          <t>-6430979.648412267</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-6375046.039764259</t>
+          <t>-6293886.04695791</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>11143003</v>
+        <v>16016019</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.42</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.32</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.73</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10433,17 +10433,17 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>123.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>122.3</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>118.54</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>118.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>52557.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>49543.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>49543.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>68693.1</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>83815.24</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>83815.24000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-9253.191269598421</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>52557</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>52557.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>122.1</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>118.31</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>118.31</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>65858.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>53388.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>53388.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>77385.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>83948.7</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>83948.7</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-9073.326635570935</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>65858</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>65858.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>120.0</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>121.88</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>118.09</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>121.88</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>118.09</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>42160.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>52439.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>52439.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>101524.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>83734.12</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>83734.12</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-9917.436921404122</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>42160</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>42160.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>120.0</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>121.88</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>117.93</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>121.88</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>117.93</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>46206.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>58524.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>58524.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>103664.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>84131.76</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>84131.75999999999</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-8230.043153972802</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>46206</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>46206.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>120.1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>121.9</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>117.76</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>117.76</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>40938.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>78379.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>78379</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>108411.7</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>83812.18</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>83812.17999999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-5959.050516429023</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>40938</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>40938.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>121.1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>121.85</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>117.54</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>121.85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>117.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>71781.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>87842.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>87842.39999999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>118042.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>83455.92</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>83455.92</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1937.523515779743</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>71781</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>71781.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>122.9</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>122.15</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>117.41</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>117.41</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>61114.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>101382.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>101382.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>116651.1</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>82649.4</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>82649.39999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>572.1051821399305</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>61114</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>61114.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>124.4</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>122.2</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>117.22</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>117.22</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>72582.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>150609.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>150609.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>119029.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>81860.1</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>81860.10000000001</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>5279.749565520178</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>72582</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>72582.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>123.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>122.1</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>116.96</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>116.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>145480.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>148805.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>148805</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>121569.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>81278.2</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>81278.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>10587.67905729481</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>145480</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>145480.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>123.0</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>122.2</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>116.78</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>116.78</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>88255.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>138444.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>138444.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>112189.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>79553.16</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>79553.16</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>9981.804079212336</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>88255</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>88255.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>121.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>122.15</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>116.48</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>122.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>116.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>139483.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>148242.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>148242.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>110067.8</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>78905.26</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>78905.25999999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>14891.02539340836</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>139483</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>139483.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>54.78</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>58.02</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>54.78</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>58.02</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>16370637.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>14968564.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>14968564.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>25991927.5</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>55328963.9</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>55328963.9</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-3761738.343921479</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>16370637</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>16370637.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>55.01</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>58.25</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>58.25</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>14210191.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>15743790.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>15743790.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>25956465.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>65312254.98</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>65312254.98</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-3880161.860334959</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>14210191</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>14210191.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>55.27</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>58.46</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>15825778.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>21316600.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>21316600.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>25649746.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>67714501.66</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>67714501.66</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-3679284.745913677</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>15825778</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>15825778.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>52.14</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>58.66</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>58.66</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>17027345.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>22754558.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>22754558</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>26782636.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>69191727.6</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>69191727.59999999</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-3434013.020100649</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>17027345</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>17027345.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>52.67999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>55.92</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>58.83</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>55.92</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>58.83</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>11408872.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>28718377.4</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>28718377.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>27355481.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>69373581.34</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>69373581.34</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-3089720.839649871</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>11408872</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>11408872.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>53.23999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>56.26</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>58.96</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>58.96</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>20246765.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>37015290.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>37015290.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>28888889.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>69945836.02</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>69945836.02</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1885548.444732688</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>20246765</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>20246765.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>54.21999999999999</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>56.57</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>59.12</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>59.12</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>42074242.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>36169141.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>36169141.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>29060387.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>70323701.58</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>70323701.58</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-1044878.257539123</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>42074242</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>42074242.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>55.12</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>56.86</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>59.28</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>59.28</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>23015566.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>29982893.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>29982893.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>27325142.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>70871687.6</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>70871687.59999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-2145262.016636197</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>23015566</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>23015566.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>55.72000000000001</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>57.07</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>59.42</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>59.42</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>46846442.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>30810714.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>30810714.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>28427276.6</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>71965384.46</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>71965384.45999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-1598621.314752154</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>46846442</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>46846442.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>56.22000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>57.31</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>59.56</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>52893437.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>25992585.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>25992585.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>25254632.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>72823093.42</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>72823093.42</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-3313920.550819516</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>52893437</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>52893437.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>56.66</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>59.68</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>57.52</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>59.68</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>16016019.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>20762488.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>20762488.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>23044675.4</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>73396602.94</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>73396602.94</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-6293886.04695791</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>16016019</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>16016019.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>418.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-21.48</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-27.88</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>114.0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,211 +1014,211 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>123.9</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>118.79</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>114.88</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>16.79</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>9.61</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-88.73</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>249903.1307142857</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>46545.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>50665.2</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>64522.1</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>84233.2</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-13856</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-4483.362775524639</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-9598.66673167771</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>46545.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>17.76</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>緯軟</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>緯軟</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-4.149646613080949</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>13.20370656475155</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>10.82606207727494</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>118.54</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>114.51</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-89.20</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>250160.7639484979</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>52557.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>49543.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>68693.1</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>83815.24000000001</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-19149</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-3553.307510769535</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-9253.191269598421</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>52557.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>緯軟</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>緯軟</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-4.149646613080949</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>13.20370656475155</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>10.82606207727494</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>3.19</t>
-        </is>
-      </c>
       <c r="BU2" t="inlineStr">
         <is>
           <t>40.83</t>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>126.5</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>126.5</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>529.0</t>
+          <t>418.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-27.88</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,94 +1423,94 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>122.1</v>
+        <v>122.3</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.31</v>
+        <v>118.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>114.14</t>
+          <t>114.51</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-89.20</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>53388.6</v>
+        <v>49543.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>77385.7</t>
+          <t>68693.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>83948.7</v>
+        <v>83815.24000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-23997</t>
+          <t>-19149</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-2516.965009164283</t>
+          <t>-3553.307510769535</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9073.326635570935</t>
+          <t>-9253.191269598421</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>343.0</t>
+          <t>529.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.35</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>121.88</v>
+        <v>122.1</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.09</v>
+        <v>118.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>114.14</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>52439.8</v>
+        <v>53388.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>101524.8</t>
+          <t>77385.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>83734.12</v>
+        <v>83948.7</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-49085</t>
+          <t>-23997</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-1324.899258908528</t>
+          <t>-2516.965009164283</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9917.436921404122</t>
+          <t>-9073.326635570935</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,27 +2304,27 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2351,26 +2351,26 @@
         <v>121.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>117.93</v>
+        <v>118.09</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>58524.2</v>
+        <v>52439.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>84131.75999999999</v>
+        <v>83734.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>121.9</v>
+        <v>121.88</v>
       </c>
       <c r="AN6" t="n">
-        <v>117.76</v>
+        <v>117.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>78379</v>
+        <v>58524.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>83812.17999999999</v>
+        <v>84131.75999999999</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,42 +3033,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>4.24</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>340.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>121.5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.57</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>-2.09</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>615.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>116.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>121.85</v>
+        <v>121.9</v>
       </c>
       <c r="AN7" t="n">
-        <v>117.54</v>
+        <v>117.76</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>87842.39999999999</v>
+        <v>78379</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>83455.92</v>
+        <v>83812.17999999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>122.15</v>
+        <v>121.85</v>
       </c>
       <c r="AN8" t="n">
-        <v>117.41</v>
+        <v>117.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>101382.8</v>
+        <v>87842.39999999999</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>82649.39999999999</v>
+        <v>83455.92</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3826,7 +3826,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>122.2</v>
+        <v>122.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>117.22</v>
+        <v>117.41</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>150609.8</v>
+        <v>101382.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>81860.10000000001</v>
+        <v>82649.39999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>5279.749565520178</t>
+          <t>572.1051821399305</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,84 +4338,84 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>-2.07</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>122.1</v>
+        <v>122.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>116.96</v>
+        <v>117.22</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>148805</v>
+        <v>150609.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>81278.2</v>
+        <v>81860.10000000001</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>10587.67905729481</t>
+          <t>5279.749565520178</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.2</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,94 +4863,94 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>122.2</v>
+        <v>122.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>116.78</v>
+        <v>116.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>138444.4</v>
+        <v>148805</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>79553.16</v>
+        <v>81278.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>9981.804079212336</t>
+          <t>10587.67905729481</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1107.0</t>
+          <t>700.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>23.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,89 +5293,89 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>371</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>96.67</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>122.15</v>
+        <v>122.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>116.48</v>
+        <v>116.78</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>111.45</t>
+          <t>111.8</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-10.59</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-78.78</t>
+          <t>-78.81</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>250160.7639484979</t>
+          <t>249903.1307142857</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>148242.2</v>
+        <v>138444.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>110067.8</t>
+          <t>112189.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>78905.25999999999</v>
+        <v>79553.16</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>38174</t>
+          <t>26255</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2424.079051070275</t>
+          <t>3586.805978476746</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>14891.02539340836</t>
+          <t>9981.804079212336</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>139483.0</t>
+          <t>88255.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>18.22</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>18.98</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN13" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN14" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,42 +6604,42 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -6648,29 +6648,29 @@
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN15" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7054,53 +7054,53 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,17 +7286,17 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN19" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN20" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,39 +9199,39 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN21" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9240,17 +9240,17 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-5.74</t>
+          <t>-3.45</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.31</v>
+        <v>57.07</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.56</v>
+        <v>59.42</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>25992585.6</v>
+        <v>30810714.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>72823093.42</v>
+        <v>71965384.45999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>281.766</t>
+          <t>952.128</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.22</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-9.90</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.41</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,17 +10044,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>233</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>18.75</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10064,55 +10064,55 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>56.66</t>
+          <t>56.22000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.52</v>
+        <v>57.31</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.68</v>
+        <v>59.56</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.24</t>
+          <t>59.23</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-8.99</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
           <t>-0.88</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>-0.86</t>
-        </is>
-      </c>
       <c r="AS23" t="inlineStr">
         <is>
           <t>7.38</t>
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.62</t>
+          <t>-111.89</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>332646132.3207964</t>
+          <t>332183148.1480118</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>20762488.6</v>
+        <v>25992585.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>23044675.4</t>
+          <t>25254632.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>73396602.94</v>
+        <v>72823093.42</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-2282186</t>
+          <t>737953</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-6430979.648412267</t>
+          <t>-5951432.094936458</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-6293886.04695791</t>
+          <t>-3313920.550819516</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>16016019.0</t>
+          <t>52893437.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-5.31</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.45</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>509.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>122.48</v>
+        <v>122.58</v>
       </c>
       <c r="AN2" t="n">
-        <v>118.79</v>
+        <v>119.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>114.88</t>
+          <t>115.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.73</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>50665.2</v>
+        <v>54228.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64522.1</t>
+          <t>56376.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>84233.2</v>
+        <v>84782.52</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-13856</t>
+          <t>-2148</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4483.362775524639</t>
+          <t>-5068.973561881043</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-9598.66673167771</t>
+          <t>-8289.832886841265</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>418.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,74 +1328,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>-2.45</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-21.48</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-27.88</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>114.0</t>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,206 +1449,206 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>123.9</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>122.48</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>118.79</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>114.88</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>16.79</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>9.61</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-88.73</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>249683.6276747503</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>46545.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>50665.2</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>64522.1</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>84233.2</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-13856</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-4483.362775524639</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-9598.66673167771</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>46545.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-11-29</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/08/13</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>17.76</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>緯軟</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>緯軟</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>資訊服務業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-4.149646613080949</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>13.20370656475155</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>10.82606207727494</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
           <t>3.17</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>122.3</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>118.54</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>114.51</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>9.61</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-89.20</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>249903.1307142857</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>52557.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>49543.8</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>68693.1</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>83815.24000000001</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-19149</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-3553.307510769535</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-9253.191269598421</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>52557.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/08/13</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>16.82</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>緯軟</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>緯軟</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>資訊服務業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-4.149646613080949</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>13.20370656475155</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>10.82606207727494</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
       <c r="BU3" t="inlineStr">
         <is>
           <t>40.83</t>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>126.5</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>126.5</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>529.0</t>
+          <t>418.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-27.88</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,22 +1853,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>122.1</v>
+        <v>122.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.31</v>
+        <v>118.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>114.14</t>
+          <t>114.51</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-89.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>53388.6</v>
+        <v>49543.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>77385.7</t>
+          <t>68693.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>83948.7</v>
+        <v>83815.24000000001</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-23997</t>
+          <t>-19149</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-2516.965009164283</t>
+          <t>-3553.307510769535</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9073.326635570935</t>
+          <t>-9253.191269598421</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>343.0</t>
+          <t>529.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.35</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>121.88</v>
+        <v>122.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.09</v>
+        <v>118.31</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>114.14</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>52439.8</v>
+        <v>53388.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>101524.8</t>
+          <t>77385.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>83734.12</v>
+        <v>83948.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-49085</t>
+          <t>-23997</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-1324.899258908528</t>
+          <t>-2516.965009164283</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9917.436921404122</t>
+          <t>-9073.326635570935</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2781,26 +2781,26 @@
         <v>121.88</v>
       </c>
       <c r="AN6" t="n">
-        <v>117.93</v>
+        <v>118.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>58524.2</v>
+        <v>52439.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>84131.75999999999</v>
+        <v>83734.12</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>121.9</v>
+        <v>121.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>117.76</v>
+        <v>117.93</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>78379</v>
+        <v>58524.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>83812.17999999999</v>
+        <v>84131.75999999999</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>121.85</v>
+        <v>121.9</v>
       </c>
       <c r="AN8" t="n">
-        <v>117.54</v>
+        <v>117.76</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>87842.39999999999</v>
+        <v>78379</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>83455.92</v>
+        <v>83812.17999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>122.15</v>
+        <v>121.85</v>
       </c>
       <c r="AN9" t="n">
-        <v>117.41</v>
+        <v>117.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>101382.8</v>
+        <v>87842.39999999999</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>82649.39999999999</v>
+        <v>83455.92</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>122.2</v>
+        <v>122.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>117.22</v>
+        <v>117.41</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>150609.8</v>
+        <v>101382.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>81860.10000000001</v>
+        <v>82649.39999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>5279.749565520178</t>
+          <t>572.1051821399305</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,17 +4641,17 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,84 +4768,84 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-2.45</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>122.1</v>
+        <v>122.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>116.96</v>
+        <v>117.22</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>148805</v>
+        <v>150609.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>81278.2</v>
+        <v>81860.10000000001</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>10587.67905729481</t>
+          <t>5279.749565520178</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-4.35</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>700.0</t>
+          <t>1175.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>23.40</t>
+          <t>22.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-28 00:00:00</t>
+          <t>2025-11-29 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,22 +5293,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-4.54</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>509</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>96.67</t>
+          <t>78.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>122.2</v>
+        <v>122.1</v>
       </c>
       <c r="AN12" t="n">
-        <v>116.78</v>
+        <v>116.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>111.8</t>
+          <t>112.09</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-78.81</t>
+          <t>-79.46</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>249903.1307142857</t>
+          <t>249683.6276747503</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>138444.4</v>
+        <v>148805</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>112189.0</t>
+          <t>121569.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>79553.16</v>
+        <v>81278.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>3586.805978476746</t>
+          <t>4663.863375217987</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>9981.804079212336</t>
+          <t>10587.67905729481</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>88255.0</t>
+          <t>145480.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>18.22</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>21.81</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,68 +5744,68 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN14" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN15" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,42 +7034,42 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -7078,29 +7078,29 @@
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,17 +7716,17 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN19" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN20" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN21" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,39 +9629,39 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9670,17 +9670,17 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>952.128</t>
+          <t>859.439</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>8.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-12.20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>226</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.37</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>56.22000000000001</t>
+          <t>55.72000000000001</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.31</v>
+        <v>57.07</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.56</v>
+        <v>59.42</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-8.99</t>
+          <t>-20.32</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-111.89</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>332183148.1480118</t>
+          <t>331720689.4764706</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>25992585.6</v>
+        <v>30810714.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>25254632.5</t>
+          <t>28427276.6</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>72823093.42</v>
+        <v>71965384.45999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>737953</t>
+          <t>2383438</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-5951432.094936458</t>
+          <t>-5281768.897985027</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3313920.550819516</t>
+          <t>-1598621.314752154</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>52893437.0</t>
+          <t>46846442.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.95</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>16.51</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,42 +883,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>702.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>509.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,33 +993,33 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>122.58</v>
+        <v>122.7</v>
       </c>
       <c r="AN2" t="n">
-        <v>119.12</v>
+        <v>119.51</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>115.23</t>
+          <t>115.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>33.27</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-86.96</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>64021.0</t>
+          <t>89855.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>54228.2</v>
+        <v>63767.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>56376.2</t>
+          <t>58103.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>84782.52</v>
+        <v>86167.84</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2148</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5068.973561881043</t>
+          <t>-5093.570455943146</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-8289.832886841265</t>
+          <t>-5228.853373284714</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>64021.0</t>
+          <t>89855.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>509.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>122.48</v>
+        <v>122.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>118.79</v>
+        <v>119.12</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>114.88</t>
+          <t>115.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.73</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>50665.2</v>
+        <v>54228.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>64522.1</t>
+          <t>56376.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>84233.2</v>
+        <v>84782.52</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-13856</t>
+          <t>-2148</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4483.362775524639</t>
+          <t>-5068.973561881043</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-9598.66673167771</t>
+          <t>-8289.832886841265</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>418.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,74 +1758,74 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.56</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-21.48</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-27.88</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>114.0</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>122.3</v>
+        <v>122.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.54</v>
+        <v>118.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>114.51</t>
+          <t>114.88</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-89.20</t>
+          <t>-88.73</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>52557.0</t>
+          <t>46545.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>49543.8</v>
+        <v>50665.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>68693.1</t>
+          <t>64522.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>83815.24000000001</v>
+        <v>84233.2</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-19149</t>
+          <t>-13856</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-3553.307510769535</t>
+          <t>-4483.362775524639</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9253.191269598421</t>
+          <t>-9598.66673167771</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>52557.0</t>
+          <t>46545.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2121,27 +2121,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>126.5</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>126.5</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>529.0</t>
+          <t>418.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,27 +2198,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-27.88</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,94 +2283,94 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>122.1</v>
+        <v>122.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.31</v>
+        <v>118.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>114.14</t>
+          <t>114.51</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-89.20</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>53388.6</v>
+        <v>49543.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>77385.7</t>
+          <t>68693.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>83948.7</v>
+        <v>83815.24000000001</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-23997</t>
+          <t>-19149</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-2516.965009164283</t>
+          <t>-3553.307510769535</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9073.326635570935</t>
+          <t>-9253.191269598421</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2551,27 +2551,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>343.0</t>
+          <t>529.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-48.35</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>121.88</v>
+        <v>122.1</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.09</v>
+        <v>118.31</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>114.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>52439.8</v>
+        <v>53388.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>101524.8</t>
+          <t>77385.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>83734.12</v>
+        <v>83948.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-49085</t>
+          <t>-23997</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-1324.899258908528</t>
+          <t>-2516.965009164283</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9917.436921404122</t>
+          <t>-9073.326635570935</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2981,27 +2981,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.37</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,27 +3164,27 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3211,26 +3211,26 @@
         <v>121.88</v>
       </c>
       <c r="AN7" t="n">
-        <v>117.93</v>
+        <v>118.09</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>58524.2</v>
+        <v>52439.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>84131.75999999999</v>
+        <v>83734.12</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>121.9</v>
+        <v>121.88</v>
       </c>
       <c r="AN8" t="n">
-        <v>117.76</v>
+        <v>117.93</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>78379</v>
+        <v>58524.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>83812.17999999999</v>
+        <v>84131.75999999999</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3841,27 +3841,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>121.85</v>
+        <v>121.9</v>
       </c>
       <c r="AN9" t="n">
-        <v>117.54</v>
+        <v>117.76</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>87842.39999999999</v>
+        <v>78379</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>83455.92</v>
+        <v>83812.17999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4271,27 +4271,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>122.15</v>
+        <v>121.85</v>
       </c>
       <c r="AN10" t="n">
-        <v>117.41</v>
+        <v>117.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>101382.8</v>
+        <v>87842.39999999999</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>82649.39999999999</v>
+        <v>83455.92</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4701,27 +4701,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>7.03</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>122.2</v>
+        <v>122.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>117.22</v>
+        <v>117.41</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>150609.8</v>
+        <v>101382.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>81860.10000000001</v>
+        <v>82649.39999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>5279.749565520178</t>
+          <t>572.1051821399305</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5131,27 +5131,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1175.0</t>
+          <t>592.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,84 +5198,84 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>122.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>26.53</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>-2.45</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>22.40</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>121.0</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-4.54</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>702</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>78.33</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>123.2</t>
+          <t>124.4</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>122.1</v>
+        <v>122.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>116.96</v>
+        <v>117.22</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>112.09</t>
+          <t>112.42</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-16.29</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-79.46</t>
+          <t>-80.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>249683.6276747503</t>
+          <t>249519.9508547009</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>148805</v>
+        <v>150609.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>121569.0</t>
+          <t>119029.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>81278.2</v>
+        <v>81860.10000000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>27236</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4663.863375217987</t>
+          <t>4758.61509680294</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>10587.67905729481</t>
+          <t>5279.749565520178</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>145480.0</t>
+          <t>72582.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>19.28</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>21.79</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右上上櫃</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,102 +6068,102 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-23.55</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>-50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-08-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>63.8</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>61.5</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>59.6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-14.63</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>7.05</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
           <t>0.57</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>-31.01</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-09-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-08-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>63.8</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>62.5</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>59.6</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>-15.12</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>7.05</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>-1.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,68 +6174,68 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN15" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,53 +7110,53 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,42 +7464,42 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -7508,29 +7508,29 @@
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN19" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN20" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN21" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>859.439</t>
+          <t>429.632</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.38</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.20</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>270</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,39 +10059,39 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>55.72000000000001</t>
+          <t>55.12</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>57.07</v>
+        <v>56.86</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.42</v>
+        <v>59.28</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10100,17 +10100,17 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-20.32</t>
+          <t>-28.39</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-113.48</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/06</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>331720689.4764706</t>
+          <t>331265030.4933921</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>30810714.6</v>
+        <v>29982893.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>28427276.6</t>
+          <t>27325142.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>71965384.45999999</v>
+        <v>70871687.59999999</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2383438</t>
+          <t>2657750</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-5281768.897985027</t>
+          <t>-4799229.377777515</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1598621.314752154</t>
+          <t>-2145262.016636197</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>46846442.0</t>
+          <t>23015566.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-8.73</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.95</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>16.54</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.66</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>702.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>126.1</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>122.7</v>
+        <v>123.08</v>
       </c>
       <c r="AN2" t="n">
-        <v>119.51</v>
+        <v>119.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>115.59</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>33.27</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-86.96</t>
+          <t>-85.30</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>89855.0</t>
+          <t>155750.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>63767.2</v>
+        <v>81745.60000000001</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>58103.5</t>
+          <t>67567.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>86167.84</v>
+        <v>88550.08</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-5093.570455943146</t>
+          <t>-4004.301367253895</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-5228.853373284714</t>
+          <t>1986.678620536986</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>89855.0</t>
+          <t>155750.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>509.0</t>
+          <t>702.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,33 +1423,33 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>122.58</v>
+        <v>122.7</v>
       </c>
       <c r="AN3" t="n">
-        <v>119.12</v>
+        <v>119.51</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>115.23</t>
+          <t>115.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>33.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-86.96</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>64021.0</t>
+          <t>89855.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>54228.2</v>
+        <v>63767.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>56376.2</t>
+          <t>58103.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>84782.52</v>
+        <v>86167.84</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2148</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5068.973561881043</t>
+          <t>-5093.570455943146</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8289.832886841265</t>
+          <t>-5228.853373284714</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>64021.0</t>
+          <t>89855.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>509.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>122.48</v>
+        <v>122.58</v>
       </c>
       <c r="AN4" t="n">
-        <v>118.79</v>
+        <v>119.12</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>114.88</t>
+          <t>115.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.73</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>50665.2</v>
+        <v>54228.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>64522.1</t>
+          <t>56376.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>84233.2</v>
+        <v>84782.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-13856</t>
+          <t>-2148</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-4483.362775524639</t>
+          <t>-5068.973561881043</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9598.66673167771</t>
+          <t>-8289.832886841265</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>418.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,74 +2188,74 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-1.63</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-21.48</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>-1.05</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-27.88</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>114.0</t>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>122.3</v>
+        <v>122.48</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.54</v>
+        <v>118.79</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>114.51</t>
+          <t>114.88</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-89.20</t>
+          <t>-88.73</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>52557.0</t>
+          <t>46545.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>49543.8</v>
+        <v>50665.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>68693.1</t>
+          <t>64522.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>83815.24000000001</v>
+        <v>84233.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-19149</t>
+          <t>-13856</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-3553.307510769535</t>
+          <t>-4483.362775524639</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9253.191269598421</t>
+          <t>-9598.66673167771</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>52557.0</t>
+          <t>46545.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>126.5</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>126.5</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>529.0</t>
+          <t>418.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,27 +2628,27 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-27.88</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,94 +2713,94 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>122.1</v>
+        <v>122.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.31</v>
+        <v>118.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>114.14</t>
+          <t>114.51</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-89.20</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>53388.6</v>
+        <v>49543.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>77385.7</t>
+          <t>68693.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>83948.7</v>
+        <v>83815.24000000001</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-23997</t>
+          <t>-19149</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-2516.965009164283</t>
+          <t>-3553.307510769535</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9073.326635570935</t>
+          <t>-9253.191269598421</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>343.0</t>
+          <t>529.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-48.35</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>121.88</v>
+        <v>122.1</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.09</v>
+        <v>118.31</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>114.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>52439.8</v>
+        <v>53388.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>101524.8</t>
+          <t>77385.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>83734.12</v>
+        <v>83948.7</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-49085</t>
+          <t>-23997</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-1324.899258908528</t>
+          <t>-2516.965009164283</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9917.436921404122</t>
+          <t>-9073.326635570935</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,27 +3594,27 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3641,26 +3641,26 @@
         <v>121.88</v>
       </c>
       <c r="AN8" t="n">
-        <v>117.93</v>
+        <v>118.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>58524.2</v>
+        <v>52439.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>84131.75999999999</v>
+        <v>83734.12</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>121.9</v>
+        <v>121.88</v>
       </c>
       <c r="AN9" t="n">
-        <v>117.76</v>
+        <v>117.93</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>78379</v>
+        <v>58524.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>83812.17999999999</v>
+        <v>84131.75999999999</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>121.85</v>
+        <v>121.9</v>
       </c>
       <c r="AN10" t="n">
-        <v>117.54</v>
+        <v>117.76</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>87842.39999999999</v>
+        <v>78379</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>83455.92</v>
+        <v>83812.17999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.03</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>122.15</v>
+        <v>121.85</v>
       </c>
       <c r="AN11" t="n">
-        <v>117.41</v>
+        <v>117.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>101382.8</v>
+        <v>87842.39999999999</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>82649.39999999999</v>
+        <v>83455.92</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>592.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>-13.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-02 00:00:00</t>
+          <t>2025-12-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>43.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>4.21</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>124.4</t>
+          <t>122.9</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>122.2</v>
+        <v>122.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>117.22</v>
+        <v>117.41</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>112.42</t>
+          <t>112.67</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.29</t>
+          <t>-32.54</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-80.26</t>
+          <t>-81.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>249519.9508547009</t>
+          <t>249497.3406827881</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>150609.8</v>
+        <v>101382.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>119029.5</t>
+          <t>116651.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>81860.10000000001</v>
+        <v>82649.39999999999</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>31580</t>
+          <t>-15268</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4758.61509680294</t>
+          <t>4114.536648393246</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>5279.749565520178</t>
+          <t>572.1051821399305</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>72582.0</t>
+          <t>61114.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>21.79</t>
+          <t>21.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,68 +6604,68 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN16" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,42 +7894,42 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -7938,29 +7938,29 @@
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN19" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,17 +8576,17 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN20" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>392.184</t>
+          <t>217.689</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN21" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN22" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-2.64</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>429.632</t>
+          <t>804.698</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-13.33</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.28</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-4.15</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.31</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>54.21999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>56.86</v>
+        <v>56.57</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.28</v>
+        <v>59.12</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.15</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-28.39</t>
+          <t>-37.13</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-113.48</t>
+          <t>-114.86</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>331265030.4933921</t>
+          <t>330804763.1502933</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>29982893.4</v>
+        <v>36169141.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>27325142.8</t>
+          <t>29060387.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>70871687.59999999</v>
+        <v>70323701.58</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>2657750</t>
+          <t>7108753</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4799229.377777515</t>
+          <t>-4221636.897740839</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-2145262.016636197</t>
+          <t>-1044878.257539123</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>23015566.0</t>
+          <t>42074242.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.66</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1185.0</t>
+          <t>402.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>123.08</v>
+        <v>123.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>119.94</v>
+        <v>120.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>116.38</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>49.43</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-85.30</t>
+          <t>-83.23</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>155750.0</t>
+          <t>52839.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>81745.60000000001</v>
+        <v>81802</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>67567.1</t>
+          <t>65672.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>88550.08</v>
+        <v>89336.96000000001</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-4004.301367253895</t>
+          <t>-3500.630533722719</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>1986.678620536986</t>
+          <t>-730.4409493012499</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>155750.0</t>
+          <t>52839.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>702.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>126.1</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>122.7</v>
+        <v>123.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>119.51</v>
+        <v>119.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>115.59</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>33.27</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-86.96</t>
+          <t>-85.30</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>89855.0</t>
+          <t>155750.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>63767.2</v>
+        <v>81745.60000000001</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>58103.5</t>
+          <t>67567.1</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>86167.84</v>
+        <v>88550.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-5093.570455943146</t>
+          <t>-4004.301367253895</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-5228.853373284714</t>
+          <t>1986.678620536986</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>89855.0</t>
+          <t>155750.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>509.0</t>
+          <t>702.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,33 +1853,33 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>98.15</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>122.58</v>
+        <v>122.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>119.12</v>
+        <v>119.51</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>115.23</t>
+          <t>115.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>22.87</t>
+          <t>33.27</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-88.05</t>
+          <t>-86.96</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>64021.0</t>
+          <t>89855.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>54228.2</v>
+        <v>63767.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>56376.2</t>
+          <t>58103.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>84782.52</v>
+        <v>86167.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2148</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5068.973561881043</t>
+          <t>-5093.570455943146</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-8289.832886841265</t>
+          <t>-5228.853373284714</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>64021.0</t>
+          <t>89855.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>17.76</t>
+          <t>19.63</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>371.0</t>
+          <t>509.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-21.48</t>
+          <t>-3.81</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,58 +2319,58 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>94.81</t>
+          <t>98.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>122.48</v>
+        <v>122.58</v>
       </c>
       <c r="AN5" t="n">
-        <v>118.79</v>
+        <v>119.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>114.88</t>
+          <t>115.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>16.79</t>
+          <t>22.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-88.73</t>
+          <t>-88.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>50665.2</v>
+        <v>54228.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>64522.1</t>
+          <t>56376.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>84233.2</v>
+        <v>84782.52</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-13856</t>
+          <t>-2148</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-4483.362775524639</t>
+          <t>-5068.973561881043</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9598.66673167771</t>
+          <t>-8289.832886841265</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>46545.0</t>
+          <t>64021.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>418.0</t>
+          <t>371.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,74 +2618,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4.18</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-21.48</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-10-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>4.21</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>-1.63</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-27.88</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-01 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-10-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>114.0</t>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>81.48</t>
+          <t>94.81</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>122.3</v>
+        <v>122.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>118.54</v>
+        <v>118.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>114.51</t>
+          <t>114.88</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>16.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-89.20</t>
+          <t>-88.73</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>52557.0</t>
+          <t>46545.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>49543.8</v>
+        <v>50665.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>68693.1</t>
+          <t>64522.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>83815.24000000001</v>
+        <v>84233.2</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-19149</t>
+          <t>-13856</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-3553.307510769535</t>
+          <t>-4483.362775524639</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-9253.191269598421</t>
+          <t>-9598.66673167771</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>52557.0</t>
+          <t>46545.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>17.76</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>126.5</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>126.5</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>529.0</t>
+          <t>418.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-27.88</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,94 +3143,94 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>63.33</t>
+          <t>81.48</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>121.3</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>122.1</v>
+        <v>122.3</v>
       </c>
       <c r="AN7" t="n">
-        <v>118.31</v>
+        <v>118.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>114.14</t>
+          <t>114.51</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-14.38</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-89.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>53388.6</v>
+        <v>49543.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>77385.7</t>
+          <t>68693.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>83948.7</v>
+        <v>83815.24000000001</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-23997</t>
+          <t>-19149</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-2516.965009164283</t>
+          <t>-3553.307510769535</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-9073.326635570935</t>
+          <t>-9253.191269598421</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>65858.0</t>
+          <t>52557.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>343.0</t>
+          <t>529.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-48.35</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>63.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.3</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>121.88</v>
+        <v>122.1</v>
       </c>
       <c r="AN8" t="n">
-        <v>118.09</v>
+        <v>118.31</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>113.78</t>
+          <t>114.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-44.30</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-88.87</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>52439.8</v>
+        <v>53388.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>101524.8</t>
+          <t>77385.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>83734.12</v>
+        <v>83948.7</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-49085</t>
+          <t>-23997</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-1324.899258908528</t>
+          <t>-2516.965009164283</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-9917.436921404122</t>
+          <t>-9073.326635570935</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>42160.0</t>
+          <t>65858.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>17.29</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>122.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>386.0</t>
+          <t>343.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.54</t>
+          <t>-48.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,27 +4024,27 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.35</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4071,26 +4071,26 @@
         <v>121.88</v>
       </c>
       <c r="AN9" t="n">
-        <v>117.93</v>
+        <v>118.09</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>113.47</t>
+          <t>113.78</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-55.83</t>
+          <t>-44.30</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-87.64</t>
+          <t>-88.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>58524.2</v>
+        <v>52439.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>103664.6</t>
+          <t>101524.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>84131.75999999999</v>
+        <v>83734.12</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-45140</t>
+          <t>-49085</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>237.3803160906709</t>
+          <t>-1324.899258908528</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-8230.043153972802</t>
+          <t>-9917.436921404122</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>46206.0</t>
+          <t>42160.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>12.62</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>121.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>120.5</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>340.0</t>
+          <t>386.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-27.70</t>
+          <t>-43.54</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>121.9</v>
+        <v>121.88</v>
       </c>
       <c r="AN10" t="n">
-        <v>117.76</v>
+        <v>117.93</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>113.2</t>
+          <t>113.47</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-53.45</t>
+          <t>-55.83</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-85.92</t>
+          <t>-87.64</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>78379</v>
+        <v>58524.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>108411.7</t>
+          <t>103664.6</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>83812.17999999999</v>
+        <v>84131.75999999999</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-30032</t>
+          <t>-45140</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1776.911856102212</t>
+          <t>237.3803160906709</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-5959.050516429023</t>
+          <t>-8230.043153972802</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>40938.0</t>
+          <t>46206.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>12.62</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>118.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>118.0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>120.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>615.0</t>
+          <t>340.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>-27.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>28.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>121.1</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>121.85</v>
+        <v>121.9</v>
       </c>
       <c r="AN11" t="n">
-        <v>117.54</v>
+        <v>117.76</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>112.9</t>
+          <t>113.2</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-57.39</t>
+          <t>-53.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-84.04</t>
+          <t>-85.92</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>87842.39999999999</v>
+        <v>78379</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>118042.3</t>
+          <t>108411.7</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>83455.92</v>
+        <v>83812.17999999999</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-30199</t>
+          <t>-30032</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>3183.450469289709</t>
+          <t>1776.911856102212</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-1937.523515779743</t>
+          <t>-5959.050516429023</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>71781.0</t>
+          <t>40938.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>8.88</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>119.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>507.0</t>
+          <t>615.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>11.41</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.09</t>
+          <t>-25.58</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>402</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>28.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>122.9</t>
+          <t>121.1</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>122.15</v>
+        <v>121.85</v>
       </c>
       <c r="AN12" t="n">
-        <v>117.41</v>
+        <v>117.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>112.67</t>
+          <t>112.9</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-32.54</t>
+          <t>-57.39</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-81.74</t>
+          <t>-84.04</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>249497.3406827881</t>
+          <t>249255.5241477273</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>101382.8</v>
+        <v>87842.39999999999</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>116651.1</t>
+          <t>118042.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>82649.39999999999</v>
+        <v>83455.92</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-15268</t>
+          <t>-30199</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>4114.536648393246</t>
+          <t>3183.450469289709</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>572.1051821399305</t>
+          <t>-1937.523515779743</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>61114.0</t>
+          <t>71781.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>8.88</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>21.84</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>119.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>114.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>119.0</t>
+          <t>116.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>243.53</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>52.3</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>219.546</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-8.63</t>
+          <t>-8.87</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.47</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,42 +5744,42 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.56</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-6.13</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -5788,29 +5788,29 @@
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>53.82</v>
+        <v>53.55</v>
       </c>
       <c r="AN13" t="n">
-        <v>57.26</v>
+        <v>57.04</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>58.43</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>10.30</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-122.09</t>
+          <t>-121.53</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>13243561.4</v>
+        <v>12528723.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14493675.8</t>
+          <t>13748644.2</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>39880117.8</v>
+        <v>37439432.96</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1250114</t>
+          <t>-1219920</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-3735190.270685619</t>
+          <t>-3676467.679225326</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-3586614.090894589</t>
+          <t>-3353493.426193714</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>11575135.0</t>
+          <t>12796449.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>270.323</t>
+          <t>219.546</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-21.51</t>
+          <t>-8.63</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-5.88</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.44</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>54.05</v>
+        <v>53.82</v>
       </c>
       <c r="AN14" t="n">
-        <v>57.43</v>
+        <v>57.26</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>58.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-122.55</t>
+          <t>-122.09</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>13770572.6</v>
+        <v>13243561.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17543586.5</t>
+          <t>14493675.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>40909066.6</v>
+        <v>39880117.8</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3773013</t>
+          <t>-1250114</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-3762204.121556715</t>
+          <t>-3735190.270685619</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3660695.180078171</t>
+          <t>-3586614.090894589</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>14277948.0</t>
+          <t>11575135.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>225.533</t>
+          <t>270.323</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-21.51</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-14.47</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>60.68</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.20</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.73</t>
+          <t>-5.88</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>52.04</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>54.32</v>
+        <v>54.05</v>
       </c>
       <c r="AN15" t="n">
-        <v>57.62</v>
+        <v>57.43</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>58.63</t>
+          <t>58.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.69</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-122.79</t>
+          <t>-122.55</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>14080138.6</v>
+        <v>13770572.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>18417348.3</t>
+          <t>17543586.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>42382898.78</v>
+        <v>40909066.6</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-4337209</t>
+          <t>-3773013</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-3780660.292734632</t>
+          <t>-3762204.121556715</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-3925373.301051926</t>
+          <t>-3660695.180078171</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>11807501.0</t>
+          <t>14277948.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-9.93</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>232.681</t>
+          <t>225.533</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-23.55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,7 +7013,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,68 +7034,68 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>60.68</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.64</t>
+          <t>-5.73</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>52.04</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>54.56</v>
+        <v>54.32</v>
       </c>
       <c r="AN16" t="n">
-        <v>57.82</v>
+        <v>57.62</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>58.72</t>
+          <t>58.63</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-1.69</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-122.75</t>
+          <t>-122.79</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>15124107.4</v>
+        <v>14080138.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>21921242.4</t>
+          <t>18417348.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>45541967.12</v>
+        <v>42382898.78</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-6797134</t>
+          <t>-4337209</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-3754348.836676942</t>
+          <t>-3780660.292734632</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-3898602.248834006</t>
+          <t>-3925373.301051926</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>12186586.0</t>
+          <t>11807501.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>312.769</t>
+          <t>232.681</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-42.41</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-14.96</t>
+          <t>-15.12</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>17.35</t>
+          <t>32.35</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.59</t>
+          <t>-5.64</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>51.86</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>54.78</v>
+        <v>54.56</v>
       </c>
       <c r="AN17" t="n">
-        <v>58.02</v>
+        <v>57.82</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>58.72</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-11.93</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-122.39</t>
+          <t>-122.75</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>14968564.6</v>
+        <v>15124107.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>25991927.5</t>
+          <t>21921242.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>55328963.9</v>
+        <v>45541967.12</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-11023362</t>
+          <t>-6797134</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-3728120.943557476</t>
+          <t>-3754348.836676942</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-3761738.343921479</t>
+          <t>-3898602.248834006</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>16370637.0</t>
+          <t>12186586.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>53.2</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>52.1</t>
-        </is>
-      </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>274.793</t>
+          <t>312.769</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-39.35</t>
+          <t>-42.41</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-14.96</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>37.04</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.35</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.94</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.58</t>
+          <t>-5.59</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>51.73999999999999</t>
+          <t>51.86</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>55.01</v>
+        <v>54.78</v>
       </c>
       <c r="AN18" t="n">
-        <v>58.25</v>
+        <v>58.02</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-19.37</t>
+          <t>-11.93</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.60</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-121.72</t>
+          <t>-122.39</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>15743790.2</v>
+        <v>14968564.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>25956465.7</t>
+          <t>25991927.5</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>65312254.98</v>
+        <v>55328963.9</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-10212675</t>
+          <t>-11023362</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-3722008.688945839</t>
+          <t>-3728120.943557476</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3880161.860334959</t>
+          <t>-3761738.343921479</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>14210191.0</t>
+          <t>16370637.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
           <t>52.1</t>
         </is>
       </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
-      </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>307.156</t>
+          <t>274.793</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-16.89</t>
+          <t>-39.35</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-16.59</t>
+          <t>-15.61</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,42 +8324,42 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-6.39</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.45</t>
+          <t>-5.58</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -8368,29 +8368,29 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>55.27</v>
+        <v>55.01</v>
       </c>
       <c r="AN19" t="n">
-        <v>58.46</v>
+        <v>58.25</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-19.37</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-120.67</t>
+          <t>-121.72</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>21316600.4</v>
+        <v>15743790.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>25649746.9</t>
+          <t>25956465.7</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>67714501.66</v>
+        <v>65312254.98</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-4333146</t>
+          <t>-10212675</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-3693253.56687509</t>
+          <t>-3722008.688945839</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-3679284.745913677</t>
+          <t>-3880161.860334959</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>15825778.0</t>
+          <t>14210191.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.13</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
+          <t>52.0</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>52.1</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>51.4</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
           <t>51.9</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>51.9</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>51.3</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>51.3</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>330.94</t>
+          <t>307.156</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-15.04</t>
+          <t>-16.89</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.39</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.45</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>52.14</t>
+          <t>51.73999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>55.59</v>
+        <v>55.27</v>
       </c>
       <c r="AN20" t="n">
-        <v>58.66</v>
+        <v>58.46</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>58.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-30.14</t>
+          <t>-26.31</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-119.31</t>
+          <t>-120.67</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>22754558</v>
+        <v>21316600.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>26782636.3</t>
+          <t>25649746.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>69191727.59999999</v>
+        <v>67714501.66</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-4028078</t>
+          <t>-4333146</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-3695793.352504438</t>
+          <t>-3693253.56687509</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-3434013.020100649</t>
+          <t>-3679284.745913677</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>17027345.0</t>
+          <t>15825778.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,17 +9006,17 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>217.689</t>
+          <t>330.94</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>-15.04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-14.63</t>
+          <t>-16.59</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.80</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>52.67999999999999</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>55.92</v>
+        <v>55.59</v>
       </c>
       <c r="AN21" t="n">
-        <v>58.83</v>
+        <v>58.66</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>59.06</t>
+          <t>58.97</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-31.69</t>
+          <t>-30.14</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-117.86</t>
+          <t>-119.31</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>28718377.4</v>
+        <v>22754558</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>27355481.5</t>
+          <t>26782636.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>69373581.34</v>
+        <v>69191727.59999999</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1362895</t>
+          <t>-4028078</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-3743389.776577854</t>
+          <t>-3695793.352504438</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-3089720.839649871</t>
+          <t>-3434013.020100649</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>11408872.0</t>
+          <t>17027345.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-10.10</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,42 +9483,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>217.689</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
           <t>-0.38</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>392.184</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>51.7</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-15.93</t>
+          <t>-14.63</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.33</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.37</t>
+          <t>-5.80</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.58</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>53.23999999999999</t>
+          <t>52.67999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>56.26</v>
+        <v>55.92</v>
       </c>
       <c r="AN22" t="n">
-        <v>58.96</v>
+        <v>58.83</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>59.09</t>
+          <t>59.06</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-38.48</t>
+          <t>-31.69</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-116.44</t>
+          <t>-117.86</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>37015290.4</v>
+        <v>28718377.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>28888889.5</t>
+          <t>27355481.5</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>69945836.02</v>
+        <v>69373581.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>8126400</t>
+          <t>1362895</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-3862238.674201123</t>
+          <t>-3743389.776577854</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-1885548.444732688</t>
+          <t>-3089720.839649871</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>20246765.0</t>
+          <t>11408872.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-11.47</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>51.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.64</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>804.698</t>
+          <t>392.184</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-15.61</t>
+          <t>-15.93</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>244</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.28</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.15</t>
+          <t>-5.37</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.31</t>
+          <t>-4.58</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>54.21999999999999</t>
+          <t>53.23999999999999</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>56.57</v>
+        <v>56.26</v>
       </c>
       <c r="AN23" t="n">
-        <v>59.12</v>
+        <v>58.96</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>59.09</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-37.13</t>
+          <t>-38.48</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-114.86</t>
+          <t>-116.44</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>330804763.1502933</t>
+          <t>330348525.830161</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>36169141.2</v>
+        <v>37015290.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>29060387.7</t>
+          <t>28888889.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>70323701.58</v>
+        <v>69945836.02</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>7108753</t>
+          <t>8126400</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-4221636.897740839</t>
+          <t>-3862238.674201123</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1044878.257539123</t>
+          <t>-1885548.444732688</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>42074242.0</t>
+          <t>20246765.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-11.13</t>
+          <t>-11.47</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>16.54</t>
+          <t>16.45</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>28.47</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>51.7</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/數位銀行.xlsx
+++ b/Result/checksun_type/數位銀行.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>402.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>27.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>128.4</t>
+          <t>129.9</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>123.6</v>
+        <v>124.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>120.38</v>
+        <v>120.85</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>116.38</t>
+          <t>116.76</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>49.43</t>
+          <t>52.14</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-83.23</t>
+          <t>-80.71</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>249255.5241477273</t>
+          <t>249075.9191489362</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>52839.0</t>
+          <t>81756.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>81802</v>
+        <v>88844.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>65672.9</t>
+          <t>69754.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>89336.96000000001</v>
+        <v>90641.89999999999</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-3500.630533722719</t>
+          <t>-3030.593316912376</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-730.4409493012499</t>
+          <t>-445.3886244554888</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>52839.0</t>
+          <t>81756.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>22.90</t>
+          <t>24.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>132.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1185.0</t>
+          <t>402.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>24.56</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.97</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>127.1</t>
+          <t>128.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>123.08</v>
+        <v>123.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>119.94</v>
+        <v>120.38</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>115.97</t>
+          <t>116.38</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>49.43</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-85.30</t>
+          <t>-83.23</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>249255.5241477273</t>
+          <t>249075.9191489362</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>155750.0</t>
+          <t>52839.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>81745.60000000001</v>
+        <v>81802</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>67567.1</t>
+          <t>65672.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>88550.08</v>
+        <v>89336.96000000001</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-4004.301367253895</t>
+          <t>-3500.630533722719</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1986.678620536986</t>
+          <t>-730.4409493012499</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>155750.0</t>
+          <t>52839.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>22.90</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>702.0</t>
+          <t>1185.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.75</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>4.40</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>9.97</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>612</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>126.1</t>
+          <t>127.1</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>122.7</v>
+        <v>123.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>119.51</v>
+        <v>119.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>115.59</t>
+          <t>115.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>33.27</t>
+          <t>45.28</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-86.96</t>
+          <t>-85.30</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>249255.5241477273</t>
+          <t>249075.9191489362</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>89855.0</t>
+          <t>155750.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>63767.2</v>
+        <v>81745.60000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>58103.5</t>
+          <t>67567.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>86167.84</v>
+        <v>88550.08</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-5093.570455943146</t>
+          <t>-4004.301367253895</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-5228.853373284714</t>
+          <t>1986.678620536986</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>89855.0</t>
+          <t>155750.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>19.63</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>22.02</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9619</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>133.5</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>509.0</t>
+          <t>702.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-3.81</t>
+          <t>9.75</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-04 00:00:00</t>
+          <t>2025-12-05 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2283,33 +2283,33 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
  